--- a/ejemplo/Ejemplo_ARQ.xlsx
+++ b/ejemplo/Ejemplo_ARQ.xlsx
@@ -43,35 +43,60 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tamaño MEP</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Longitud (m)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área (m²)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área bruta (m²)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Volumen (m³)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Longitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Volumen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t xml:space="preserve">Área</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Coste</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Código de montaje</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Descripción de montaje</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Resistencia al fuego</t>
         </is>
@@ -108,37 +133,49 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2">
+        <v>20.0</v>
+      </c>
+      <c r="I2">
+        <v>48.45</v>
+      </c>
+      <c r="J2">
+        <v>57.0</v>
+      </c>
+      <c r="K2">
+        <v>14.25</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">20,00 m</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">14,25 m³</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57,00 m²</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48,45 m²</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -175,37 +212,49 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3">
+        <v>20.0</v>
+      </c>
+      <c r="I3">
+        <v>48.45</v>
+      </c>
+      <c r="J3">
+        <v>57.0</v>
+      </c>
+      <c r="K3">
+        <v>14.25</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">20,00 m</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">14,25 m³</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57,00 m²</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48,45 m²</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -242,37 +291,49 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4">
+        <v>12.0</v>
+      </c>
+      <c r="I4">
+        <v>29.07</v>
+      </c>
+      <c r="J4">
+        <v>34.2</v>
+      </c>
+      <c r="K4">
+        <v>8.55</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">12,00 m</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">8,55 m³</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34,20 m²</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29,07 m²</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -309,37 +370,49 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5">
+        <v>12.0</v>
+      </c>
+      <c r="I5">
+        <v>29.07</v>
+      </c>
+      <c r="J5">
+        <v>34.2</v>
+      </c>
+      <c r="K5">
+        <v>8.55</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">12,00 m</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">8,55 m³</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34,20 m²</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29,07 m²</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -376,32 +449,44 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6">
+        <v>19.5</v>
+      </c>
+      <c r="I6">
+        <v>55.58</v>
+      </c>
+      <c r="J6">
+        <v>55.575</v>
+      </c>
+      <c r="K6">
+        <v>5.56</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">19,50 m</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">5,56 m³</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">55,58 m²</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t xml:space="preserve">C1010</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t xml:space="preserve">Tabiques</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 60</t>
         </is>
@@ -438,32 +523,44 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7">
+        <v>5.7</v>
+      </c>
+      <c r="I7">
+        <v>16.25</v>
+      </c>
+      <c r="J7">
+        <v>16.245</v>
+      </c>
+      <c r="K7">
+        <v>1.62</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">5,70 m</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">1,62 m³</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">16,25 m²</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t xml:space="preserve">C1010</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t xml:space="preserve">Tabiques</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 60</t>
         </is>
@@ -500,37 +597,49 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8">
+        <v>20.0</v>
+      </c>
+      <c r="I8">
+        <v>48.45</v>
+      </c>
+      <c r="J8">
+        <v>57.0</v>
+      </c>
+      <c r="K8">
+        <v>14.25</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">20,00 m</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">14,25 m³</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57,00 m²</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48,45 m²</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -567,37 +676,49 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9">
+        <v>20.0</v>
+      </c>
+      <c r="I9">
+        <v>48.45</v>
+      </c>
+      <c r="J9">
+        <v>57.0</v>
+      </c>
+      <c r="K9">
+        <v>14.25</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">20,00 m</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">14,25 m³</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57,00 m²</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48,45 m²</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -634,37 +755,49 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10">
+        <v>12.0</v>
+      </c>
+      <c r="I10">
+        <v>29.07</v>
+      </c>
+      <c r="J10">
+        <v>34.2</v>
+      </c>
+      <c r="K10">
+        <v>8.55</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">12,00 m</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">8,55 m³</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34,20 m²</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29,07 m²</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -701,37 +834,49 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11">
+        <v>12.0</v>
+      </c>
+      <c r="I11">
+        <v>29.07</v>
+      </c>
+      <c r="J11">
+        <v>34.2</v>
+      </c>
+      <c r="K11">
+        <v>8.55</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">12,00 m</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">8,55 m³</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34,20 m²</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29,07 m²</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -768,32 +913,44 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12">
+        <v>19.5</v>
+      </c>
+      <c r="I12">
+        <v>55.58</v>
+      </c>
+      <c r="J12">
+        <v>55.575</v>
+      </c>
+      <c r="K12">
+        <v>5.56</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">19,50 m</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">5,56 m³</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t xml:space="preserve">55,58 m²</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t xml:space="preserve">C1010</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t xml:space="preserve">Tabiques</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 60</t>
         </is>
@@ -830,32 +987,44 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13">
+        <v>5.7</v>
+      </c>
+      <c r="I13">
+        <v>16.25</v>
+      </c>
+      <c r="J13">
+        <v>16.245</v>
+      </c>
+      <c r="K13">
+        <v>1.62</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">5,70 m</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">1,62 m³</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">16,25 m²</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t xml:space="preserve">C1010</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t xml:space="preserve">Tabiques</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 60</t>
         </is>
@@ -892,37 +1061,49 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14">
+        <v>20.0</v>
+      </c>
+      <c r="I14">
+        <v>48.45</v>
+      </c>
+      <c r="J14">
+        <v>57.0</v>
+      </c>
+      <c r="K14">
+        <v>14.25</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">20,00 m</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">14,25 m³</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57,00 m²</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48,45 m²</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -959,37 +1140,49 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15">
+        <v>20.0</v>
+      </c>
+      <c r="I15">
+        <v>48.45</v>
+      </c>
+      <c r="J15">
+        <v>57.0</v>
+      </c>
+      <c r="K15">
+        <v>14.25</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">20,00 m</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">14,25 m³</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57,00 m²</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48,45 m²</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -1026,37 +1219,49 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16">
+        <v>12.0</v>
+      </c>
+      <c r="I16">
+        <v>29.07</v>
+      </c>
+      <c r="J16">
+        <v>34.2</v>
+      </c>
+      <c r="K16">
+        <v>8.55</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">12,00 m</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">8,55 m³</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34,20 m²</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29,07 m²</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -1093,37 +1298,49 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17">
+        <v>12.0</v>
+      </c>
+      <c r="I17">
+        <v>29.07</v>
+      </c>
+      <c r="J17">
+        <v>34.2</v>
+      </c>
+      <c r="K17">
+        <v>8.55</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">12,00 m</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">8,55 m³</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34,20 m²</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29,07 m²</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -1160,32 +1377,44 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18">
+        <v>19.5</v>
+      </c>
+      <c r="I18">
+        <v>55.58</v>
+      </c>
+      <c r="J18">
+        <v>55.575</v>
+      </c>
+      <c r="K18">
+        <v>5.56</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">19,50 m</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">5,56 m³</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t xml:space="preserve">55,58 m²</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t xml:space="preserve">C1010</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t xml:space="preserve">Tabiques</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 60</t>
         </is>
@@ -1222,32 +1451,44 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19">
+        <v>5.7</v>
+      </c>
+      <c r="I19">
+        <v>16.25</v>
+      </c>
+      <c r="J19">
+        <v>16.245</v>
+      </c>
+      <c r="K19">
+        <v>1.62</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">5,70 m</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">1,62 m³</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t xml:space="preserve">16,25 m²</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t xml:space="preserve">C1010</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t xml:space="preserve">Tabiques</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 60</t>
         </is>
@@ -1284,27 +1525,33 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20">
+        <v>240.0</v>
+      </c>
+      <c r="K20">
+        <v>96.0</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">96,00 m³</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t xml:space="preserve">240,00 m²</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t xml:space="preserve">110,00</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t xml:space="preserve">B3010</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t xml:space="preserve">Cubiertas</t>
         </is>

--- a/ejemplo/Ejemplo_ARQ.xlsx
+++ b/ejemplo/Ejemplo_ARQ.xlsx
@@ -68,35 +68,45 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t xml:space="preserve">W (kg/m)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peso (kg)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Longitud</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">Volumen</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t xml:space="preserve">Área</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Coste</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Código de montaje</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Descripción de montaje</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Resistencia al fuego</t>
         </is>
@@ -145,37 +155,37 @@
       <c r="K2">
         <v>14.25</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">20,00 m</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">14,25 m³</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t xml:space="preserve">48,45 m²</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -224,37 +234,37 @@
       <c r="K3">
         <v>14.25</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">20,00 m</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">14,25 m³</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t xml:space="preserve">48,45 m²</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -303,37 +313,37 @@
       <c r="K4">
         <v>8.55</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">12,00 m</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">8,55 m³</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t xml:space="preserve">29,07 m²</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -382,37 +392,37 @@
       <c r="K5">
         <v>8.55</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">12,00 m</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">8,55 m³</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t xml:space="preserve">29,07 m²</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -461,32 +471,32 @@
       <c r="K6">
         <v>5.56</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">19,50 m</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve">5,56 m³</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t xml:space="preserve">55,58 m²</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t xml:space="preserve">C1010</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t xml:space="preserve">Tabiques</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 60</t>
         </is>
@@ -535,32 +545,32 @@
       <c r="K7">
         <v>1.62</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">5,70 m</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t xml:space="preserve">1,62 m³</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t xml:space="preserve">16,25 m²</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t xml:space="preserve">C1010</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t xml:space="preserve">Tabiques</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 60</t>
         </is>
@@ -609,37 +619,37 @@
       <c r="K8">
         <v>14.25</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">20,00 m</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t xml:space="preserve">14,25 m³</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t xml:space="preserve">48,45 m²</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -688,37 +698,37 @@
       <c r="K9">
         <v>14.25</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">20,00 m</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">14,25 m³</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t xml:space="preserve">48,45 m²</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -767,37 +777,37 @@
       <c r="K10">
         <v>8.55</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t xml:space="preserve">12,00 m</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t xml:space="preserve">8,55 m³</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t xml:space="preserve">29,07 m²</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -846,37 +856,37 @@
       <c r="K11">
         <v>8.55</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t xml:space="preserve">12,00 m</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t xml:space="preserve">8,55 m³</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t xml:space="preserve">29,07 m²</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -925,32 +935,32 @@
       <c r="K12">
         <v>5.56</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t xml:space="preserve">19,50 m</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t xml:space="preserve">5,56 m³</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t xml:space="preserve">55,58 m²</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t xml:space="preserve">C1010</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t xml:space="preserve">Tabiques</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 60</t>
         </is>
@@ -999,32 +1009,32 @@
       <c r="K13">
         <v>1.62</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">5,70 m</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t xml:space="preserve">1,62 m³</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t xml:space="preserve">16,25 m²</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t xml:space="preserve">C1010</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t xml:space="preserve">Tabiques</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 60</t>
         </is>
@@ -1073,37 +1083,37 @@
       <c r="K14">
         <v>14.25</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t xml:space="preserve">20,00 m</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t xml:space="preserve">14,25 m³</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t xml:space="preserve">48,45 m²</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -1152,37 +1162,37 @@
       <c r="K15">
         <v>14.25</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t xml:space="preserve">20,00 m</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t xml:space="preserve">14,25 m³</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t xml:space="preserve">48,45 m²</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -1231,37 +1241,37 @@
       <c r="K16">
         <v>8.55</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve">12,00 m</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t xml:space="preserve">8,55 m³</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t xml:space="preserve">29,07 m²</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -1310,37 +1320,37 @@
       <c r="K17">
         <v>8.55</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t xml:space="preserve">12,00 m</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t xml:space="preserve">8,55 m³</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t xml:space="preserve">29,07 m²</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t xml:space="preserve">85,00</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t xml:space="preserve">B2010</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t xml:space="preserve">Muros exteriores</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 120</t>
         </is>
@@ -1389,32 +1399,32 @@
       <c r="K18">
         <v>5.56</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t xml:space="preserve">19,50 m</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t xml:space="preserve">5,56 m³</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t xml:space="preserve">55,58 m²</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t xml:space="preserve">C1010</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t xml:space="preserve">Tabiques</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 60</t>
         </is>
@@ -1463,32 +1473,32 @@
       <c r="K19">
         <v>1.62</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t xml:space="preserve">5,70 m</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t xml:space="preserve">1,62 m³</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t xml:space="preserve">16,25 m²</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t xml:space="preserve">C1010</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t xml:space="preserve">Tabiques</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t xml:space="preserve">EI 60</t>
         </is>
@@ -1497,12 +1507,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">310280</t>
+          <t xml:space="preserve">310315</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5e2a0004bc08-0000</t>
+          <t xml:space="preserve">5e2a0004bc2b-0000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1531,27 +1541,27 @@
       <c r="K20">
         <v>96.0</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t xml:space="preserve">96,00 m³</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t xml:space="preserve">240,00 m²</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t xml:space="preserve">110,00</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t xml:space="preserve">B3010</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t xml:space="preserve">Cubiertas</t>
         </is>
